--- a/internal_doc/05.测试设计/sdv/rest/rest_SDV分析表格.xlsx
+++ b/internal_doc/05.测试设计/sdv/rest/rest_SDV分析表格.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,6 +69,18 @@
   </si>
   <si>
     <t>createcs+creatcl+insert+queryandupdate+query+getcount+queryandremove+upsert+query+update+delete+dropcl+dropcs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10万条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发时网络长断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发时节点正常停掉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -591,8 +603,28 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" customFormat="1"/>
-    <row r="11" spans="1:7" customFormat="1"/>
+    <row r="10" spans="1:7" customFormat="1">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" customFormat="1">
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="12" spans="1:7" customFormat="1"/>
     <row r="13" spans="1:7" customFormat="1"/>
     <row r="14" spans="1:7" customFormat="1"/>
